--- a/docs/StructureDefinition-retina-diagnostic-report.xlsx
+++ b/docs/StructureDefinition-retina-diagnostic-report.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="437">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,13 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>true</t>
+    <t>false</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-30T22:57:21+01:00</t>
+    <t>2025-12-08</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -479,20 +476,20 @@
 </t>
   </si>
   <si>
-    <t>DiagnosticReport.extension:initialInstructions</t>
-  </si>
-  <si>
-    <t>initialInstructions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/RetinaIntegration/StructureDefinition/initial-instructions-extension}
+    <t>DiagnosticReport.extension:cautions</t>
+  </si>
+  <si>
+    <t>cautions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://dips.no/fhir/RetinaIntegration/StructureDefinition/cautions-extension}
 </t>
   </si>
   <si>
-    <t>Initial Instructions</t>
-  </si>
-  <si>
-    <t>Initial routing instruction and optional cautions for grading this examination (4000-series and 5000-series).</t>
+    <t>Cautions</t>
+  </si>
+  <si>
+    <t>Special considerations or cautions for grading this examination (5000-series).</t>
   </si>
   <si>
     <t>DiagnosticReport.extension:previousExaminationConclusion</t>
@@ -569,7 +566,7 @@
   </si>
   <si>
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://dips.no/fhir/NamingSystem/retina-examination-id"/&gt;
+  &lt;system value="http://dips.no/fhir/RetinaIntegration/examination-id"/&gt;
   &lt;value value="550e8400-e29b-41d4-a716-446655440000"/&gt;
 &lt;/valueIdentifier&gt;</t>
   </si>
@@ -709,7 +706,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/NamingSystem/retina-examination-id</t>
+    <t>http://dips.no/fhir/RetinaIntegration/examination-id</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -908,25 +905,13 @@
 </t>
   </si>
   <si>
-    <t>Fixed code: Bildediagnostikk</t>
-  </si>
-  <si>
-    <t>A code or name that describes this diagnostic report.</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://ehelse.no/fhir/CodeSystem/no-kodeverk-8660"/&gt;
-    &lt;code value="B"/&gt;
-    &lt;display value="Bildediagnostikk"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Codes that describe Diagnostic Reports.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/report-codes|4.0.1</t>
+    <t>Retina imaging procedure(s) performed: fundus photography and/or OCT</t>
+  </si>
+  <si>
+    <t>The type(s) of retinal imaging procedure(s) the photographer has indicated shall be performed.</t>
+  </si>
+  <si>
+    <t>http://dips.no/fhir/RetinaIntegration/ValueSet/retina-imaging-procedure-vs</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -948,17 +933,26 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1|Device|4.0.1|Location|4.0.1)
+    <t xml:space="preserve">Reference(Patient)
 </t>
   </si>
   <si>
-    <t>The subject of the report - usually, but not always, the patient</t>
-  </si>
-  <si>
-    <t>The subject of the report. Usually, but not always, this is a patient. However, diagnostic services also perform analyses on specimens collected from a variety of other sources.</t>
+    <t>Reference to the patient</t>
+  </si>
+  <si>
+    <t>A reference to the patient. The patient's identifier MUST be one of the official Norwegian patient identifier systems: Fødselsnummer (urn:oid:2.16.578.1.12.4.1.4.1), D-nummer (urn:oid:2.16.578.1.12.4.1.4.2), or Felles hjelpenummer (urn:oid:2.16.578.1.12.4.1.4.3).</t>
   </si>
   <si>
     <t>SHALL know the subject context.</t>
+  </si>
+  <si>
+    <t>&lt;valueReference xmlns="http://hl7.org/fhir"&gt;
+  &lt;reference value="Patient/cdp1000807"/&gt;
+  &lt;identifier&gt;
+    &lt;system value="urn:oid:2.16.578.1.12.4.1.4.1"/&gt;
+    &lt;value value="15076500565"/&gt;
+  &lt;/identifier&gt;
+&lt;/valueReference&gt;</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1197,38 +1191,46 @@
     <t>Optional HbA1c Laboratory Result</t>
   </si>
   <si>
-    <t>An optional observation containing HbA1c laboratory results. This observation provides important context for diabetic retinopathy assessment by documenting the patient's glycemic control status at the time of retinal examination. This value is reported by the user before the examination begins.</t>
-  </si>
-  <si>
-    <t>This slice is used to include HbA1c laboratory values that provide clinical context for retinal screening. The observation should use the SNOMED CT code 167491000202108 for HbA1c.</t>
-  </si>
-  <si>
-    <t>HbA1c values provide essential clinical context for interpreting retinal screening results and determining appropriate follow-up intervals in diabetic retinopathy management.</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.result:eyeObservation</t>
-  </si>
-  <si>
-    <t>eyeObservation</t>
+    <t>DiagnosticReport.result:dmeFinding</t>
+  </si>
+  <si>
+    <t>dmeFinding</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://dips.no/fhir/RetinaIntegration/StructureDefinition/retina-eye-observation)
+    <t xml:space="preserve">Reference(http://dips.no/fhir/RetinaIntegration/StructureDefinition/retina-diabetic-macular-edema-finding)
 </t>
   </si>
   <si>
-    <t>Optional Eye Assessment (Right or Left)</t>
-  </si>
-  <si>
-    <t>An optional observation containing diabetic retinopathy and macular edema assessment results for one eye. This observation uses components to document both DR severity and DME presence. The bodySite element identifies which eye (right or left).</t>
-  </si>
-  <si>
-    <t>This slice contains a multi-component observation for one eye with DR severity and DME presence as separate components. Up to two instances can be present (one for each eye).</t>
-  </si>
-  <si>
-    <t>Essential for tracking diabetic retinopathy and macular edema for appropriate clinical decision making and follow-up scheduling.</t>
+    <t>Optional DME Findings (up to 2: left and/or right eye). Use bodySite element to distinguish left vs right eye.</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.result:drFinding</t>
+  </si>
+  <si>
+    <t>drFinding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://dips.no/fhir/RetinaIntegration/StructureDefinition/retina-diabetic-retinopathy-finding)
+</t>
+  </si>
+  <si>
+    <t>Optional DR Findings (up to 2: left and/or right eye). Use bodySite element to distinguish left vs right eye.</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.result:imageQuality</t>
+  </si>
+  <si>
+    <t>imageQuality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://dips.no/fhir/RetinaIntegration/StructureDefinition/retina-image-quality-asessment)
+</t>
+  </si>
+  <si>
+    <t>Optional Image Quality Observations (up to 2: left and/or right eye). Use bodySite element to distinguish left vs right eye.</t>
   </si>
   <si>
     <t>DiagnosticReport.imagingStudy</t>
@@ -1364,7 +1366,7 @@
     <t>One or more codes that represent the summary conclusion (interpretation/impression) of the diagnostic report.</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/RetinaIntegration/ValueSet/retina-conclusioncode-vs</t>
+    <t>http://dips.no/fhir/RetinaIntegration/ValueSet/retina-conclusion-code-vs</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=SPRT].source[classCode=OBS, moodCode=EVN, code=LOINC:54531-9].value (type=CD)</t>
@@ -1677,15 +1679,15 @@
         <v>35</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1695,7 +1697,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN47"/>
+  <dimension ref="A1:AN49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.20703125" customWidth="true" bestFit="true"/>
@@ -1717,13 +1719,13 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="63.35546875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="60.0625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="85.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.3046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
@@ -1741,124 +1743,124 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>39</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="C1" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>41</v>
       </c>
-      <c r="D1" t="s" s="1">
+      <c r="E1" t="s" s="1">
         <v>42</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="F1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="G1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="G1" t="s" s="1">
+      <c r="H1" t="s" s="1">
         <v>45</v>
       </c>
-      <c r="H1" t="s" s="1">
+      <c r="I1" t="s" s="1">
         <v>46</v>
       </c>
-      <c r="I1" t="s" s="1">
+      <c r="J1" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="J1" t="s" s="1">
+      <c r="K1" t="s" s="1">
         <v>48</v>
       </c>
-      <c r="K1" t="s" s="1">
+      <c r="L1" t="s" s="1">
         <v>49</v>
       </c>
-      <c r="L1" t="s" s="1">
+      <c r="M1" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="M1" t="s" s="1">
+      <c r="N1" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="N1" t="s" s="1">
+      <c r="O1" t="s" s="1">
         <v>52</v>
       </c>
-      <c r="O1" t="s" s="1">
+      <c r="P1" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="P1" t="s" s="1">
+      <c r="Q1" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="Q1" t="s" s="1">
+      <c r="R1" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="R1" t="s" s="1">
+      <c r="S1" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="S1" t="s" s="1">
+      <c r="T1" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="T1" t="s" s="1">
+      <c r="U1" t="s" s="1">
         <v>58</v>
       </c>
-      <c r="U1" t="s" s="1">
+      <c r="V1" t="s" s="1">
         <v>59</v>
       </c>
-      <c r="V1" t="s" s="1">
+      <c r="W1" t="s" s="1">
         <v>60</v>
       </c>
-      <c r="W1" t="s" s="1">
+      <c r="X1" t="s" s="1">
         <v>61</v>
       </c>
-      <c r="X1" t="s" s="1">
+      <c r="Y1" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="Y1" t="s" s="1">
+      <c r="Z1" t="s" s="1">
         <v>63</v>
       </c>
-      <c r="Z1" t="s" s="1">
+      <c r="AA1" t="s" s="1">
         <v>64</v>
       </c>
-      <c r="AA1" t="s" s="1">
+      <c r="AB1" t="s" s="1">
         <v>65</v>
       </c>
-      <c r="AB1" t="s" s="1">
+      <c r="AC1" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="AC1" t="s" s="1">
+      <c r="AD1" t="s" s="1">
         <v>67</v>
       </c>
-      <c r="AD1" t="s" s="1">
+      <c r="AE1" t="s" s="1">
         <v>68</v>
       </c>
-      <c r="AE1" t="s" s="1">
+      <c r="AF1" t="s" s="1">
         <v>69</v>
       </c>
-      <c r="AF1" t="s" s="1">
+      <c r="AG1" t="s" s="1">
         <v>70</v>
       </c>
-      <c r="AG1" t="s" s="1">
+      <c r="AH1" t="s" s="1">
         <v>71</v>
       </c>
-      <c r="AH1" t="s" s="1">
+      <c r="AI1" t="s" s="1">
         <v>72</v>
       </c>
-      <c r="AI1" t="s" s="1">
+      <c r="AJ1" t="s" s="1">
         <v>73</v>
       </c>
-      <c r="AJ1" t="s" s="1">
+      <c r="AK1" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="AK1" t="s" s="1">
+      <c r="AL1" t="s" s="1">
         <v>75</v>
       </c>
-      <c r="AL1" t="s" s="1">
+      <c r="AM1" t="s" s="1">
         <v>76</v>
       </c>
-      <c r="AM1" t="s" s="1">
+      <c r="AN1" t="s" s="1">
         <v>77</v>
-      </c>
-      <c r="AN1" t="s" s="1">
-        <v>78</v>
       </c>
     </row>
     <row r="2">
@@ -1870,35 +1872,35 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G2" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="G2" t="s" s="2">
+      <c r="H2" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="H2" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s" s="2">
+      <c r="L2" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="L2" t="s" s="2">
+      <c r="M2" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="M2" t="s" s="2">
+      <c r="N2" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="N2" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -1951,25 +1953,25 @@
         <v>32</v>
       </c>
       <c r="AG2" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH2" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AH2" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI2" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK2" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="AK2" t="s" s="2">
+      <c r="AL2" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AM2" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>21</v>
@@ -1977,10 +1979,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1988,31 +1990,31 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>96</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2062,13 +2064,13 @@
         <v>21</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>21</v>
@@ -2091,10 +2093,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2102,28 +2104,28 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>101</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2174,19 +2176,19 @@
         <v>21</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>21</v>
@@ -2203,10 +2205,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2214,31 +2216,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2288,19 +2290,19 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>21</v>
@@ -2317,10 +2319,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2328,10 +2330,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>21</v>
@@ -2343,16 +2345,16 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2378,43 +2380,43 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>118</v>
-      </c>
       <c r="AG6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>21</v>
@@ -2431,21 +2433,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>21</v>
@@ -2457,16 +2459,16 @@
         <v>21</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2516,28 +2518,28 @@
         <v>21</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM7" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>126</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>21</v>
@@ -2545,22 +2547,22 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G8" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="G8" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H8" t="s" s="2">
         <v>21</v>
       </c>
@@ -2571,16 +2573,16 @@
         <v>21</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2630,28 +2632,28 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM8" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>21</v>
@@ -2659,10 +2661,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2670,10 +2672,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -2685,13 +2687,13 @@
         <v>21</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2730,29 +2732,29 @@
         <v>21</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE9" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="AF9" t="s" s="2">
+      <c r="AG9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="AG9" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ9" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>21</v>
@@ -2769,23 +2771,23 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="C10" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
@@ -2797,13 +2799,13 @@
         <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2854,19 +2856,19 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI10" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="AG10" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI10" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="AJ10" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
@@ -2883,23 +2885,23 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="C11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -2911,13 +2913,13 @@
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2968,19 +2970,19 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>21</v>
@@ -2997,23 +2999,23 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="C12" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>21</v>
@@ -3025,13 +3027,13 @@
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3082,19 +3084,19 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>21</v>
@@ -3111,10 +3113,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3122,28 +3124,28 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3194,19 +3196,19 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH13" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AH13" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>21</v>
@@ -3223,45 +3225,45 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J14" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="G14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="K14" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -3298,86 +3300,86 @@
         <v>21</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH14" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AH14" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>172</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="C15" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="B15" t="s" s="2">
+      <c r="D15" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J15" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="G15" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="K15" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="M15" t="s" s="2">
-        <v>176</v>
-      </c>
       <c r="N15" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O15" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -3390,7 +3392,7 @@
         <v>21</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="U15" t="s" s="2">
         <v>21</v>
@@ -3426,39 +3428,39 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH15" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AH15" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AM15" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>172</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3466,10 +3468,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>21</v>
@@ -3481,13 +3483,13 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3538,28 +3540,28 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>21</v>
@@ -3567,22 +3569,22 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G17" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="G17" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
       </c>
@@ -3593,16 +3595,16 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3640,31 +3642,31 @@
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE17" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="AC17" t="s" s="2">
+      <c r="AF17" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AD17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>192</v>
-      </c>
       <c r="AG17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH17" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AH17" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>21</v>
@@ -3673,7 +3675,7 @@
         <v>21</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>21</v>
@@ -3681,10 +3683,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3692,34 +3694,34 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3744,52 +3746,52 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Y18" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="Y18" t="s" s="2">
+      <c r="Z18" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="Z18" t="s" s="2">
+      <c r="AA18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AA18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF18" t="s" s="2">
+      <c r="AG18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>21</v>
@@ -3797,10 +3799,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3808,34 +3810,34 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J19" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="H19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="K19" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3860,52 +3862,52 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="Y19" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Y19" t="s" s="2">
+      <c r="Z19" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="Z19" t="s" s="2">
+      <c r="AA19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AA19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF19" t="s" s="2">
+      <c r="AG19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AG19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="AM19" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>21</v>
@@ -3913,10 +3915,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3924,34 +3926,34 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="G20" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="K20" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3961,67 +3963,67 @@
         <v>21</v>
       </c>
       <c r="S20" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="T20" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="T20" t="s" s="2">
+      <c r="U20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="U20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF20" t="s" s="2">
+      <c r="AG20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AG20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>21</v>
@@ -4029,10 +4031,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4040,31 +4042,31 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="G21" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4078,64 +4080,64 @@
         <v>21</v>
       </c>
       <c r="T21" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="U21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF21" t="s" s="2">
+      <c r="AG21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AG21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AM21" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>21</v>
@@ -4143,10 +4145,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4154,28 +4156,28 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="H22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="K22" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4226,28 +4228,28 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AG22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
@@ -4255,10 +4257,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4266,31 +4268,31 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="K23" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4340,28 +4342,28 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AG23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>21</v>
@@ -4369,22 +4371,22 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G24" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="G24" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4395,19 +4397,19 @@
         <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4456,28 +4458,28 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AG24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH24" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AH24" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>21</v>
@@ -4485,10 +4487,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4496,32 +4498,32 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I25" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="G25" t="s" s="2">
+      <c r="J25" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="K25" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4546,75 +4548,75 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="Z25" t="s" s="2">
+      <c r="AA25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK25" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AA25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK25" t="s" s="2">
+      <c r="AL25" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>272</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G26" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="G26" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4622,19 +4624,19 @@
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4660,92 +4662,92 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="Y26" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="Y26" t="s" s="2">
+      <c r="Z26" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="Z26" t="s" s="2">
+      <c r="AA26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AA26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="G27" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="K27" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4757,111 +4759,109 @@
         <v>21</v>
       </c>
       <c r="S27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Y27" s="2"/>
+      <c r="Z27" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK27" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="T27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y27" t="s" s="2">
+      <c r="AL27" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="Z27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AA27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>294</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="H28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="K28" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4874,7 +4874,7 @@
         <v>21</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>21</v>
@@ -4910,74 +4910,74 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>304</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="H29" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="K29" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -5026,74 +5026,74 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>315</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="H30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="K30" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -5142,74 +5142,74 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>326</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J31" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="H31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="K31" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5258,50 +5258,50 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>336</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5310,22 +5310,22 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5374,50 +5374,50 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AG32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH32" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AH32" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>347</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5426,22 +5426,22 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M33" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>352</v>
-      </c>
       <c r="O33" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5490,39 +5490,39 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH33" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AH33" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>346</v>
-      </c>
       <c r="AN33" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5530,11 +5530,11 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G34" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="G34" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
       </c>
@@ -5545,19 +5545,19 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5606,28 +5606,28 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH34" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AH34" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>21</v>
@@ -5635,22 +5635,22 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G35" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="G35" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H35" t="s" s="2">
         <v>21</v>
       </c>
@@ -5661,19 +5661,19 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5710,38 +5710,38 @@
         <v>21</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH35" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AH35" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>21</v>
@@ -5749,23 +5749,23 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>21</v>
@@ -5777,19 +5777,19 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -5838,28 +5838,28 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH36" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AH36" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>21</v>
@@ -5867,23 +5867,23 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>21</v>
@@ -5895,19 +5895,19 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -5956,28 +5956,28 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH37" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AH37" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>21</v>
@@ -5985,21 +5985,23 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="D38" t="s" s="2">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>375</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>21</v>
@@ -6011,18 +6013,20 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6070,28 +6074,28 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>386</v>
+        <v>359</v>
       </c>
       <c r="AG38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH38" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AH38" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>21</v>
+        <v>367</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
@@ -6099,21 +6103,23 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="D39" t="s" s="2">
-        <v>393</v>
+        <v>360</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>375</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
@@ -6122,20 +6128,22 @@
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>397</v>
+        <v>365</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6184,28 +6192,28 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>392</v>
+        <v>359</v>
       </c>
       <c r="AG39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH39" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AH39" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
@@ -6213,10 +6221,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6224,11 +6232,11 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G40" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="G40" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
       </c>
@@ -6239,15 +6247,17 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>180</v>
+        <v>387</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>181</v>
+        <v>388</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6296,19 +6306,19 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>183</v>
+        <v>386</v>
       </c>
       <c r="AG40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH40" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AH40" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
@@ -6317,7 +6327,7 @@
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>184</v>
+        <v>391</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
@@ -6325,22 +6335,22 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>187</v>
+        <v>393</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G41" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="G41" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6348,21 +6358,21 @@
         <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>136</v>
+        <v>394</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>188</v>
+        <v>395</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6410,28 +6420,28 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>192</v>
+        <v>392</v>
       </c>
       <c r="AG41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH41" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AH41" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>21</v>
+        <v>398</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>184</v>
+        <v>368</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
@@ -6439,46 +6449,42 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>402</v>
+        <v>21</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>403</v>
+        <v>180</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6526,19 +6532,19 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>406</v>
+        <v>182</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>21</v>
@@ -6547,7 +6553,7 @@
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>134</v>
+        <v>183</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
@@ -6555,22 +6561,22 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G43" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="G43" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6581,20 +6587,18 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>408</v>
+        <v>187</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>409</v>
+        <v>188</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6642,19 +6646,19 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>407</v>
+        <v>191</v>
       </c>
       <c r="AG43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH43" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AH43" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>21</v>
@@ -6663,7 +6667,7 @@
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>412</v>
+        <v>183</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -6671,42 +6675,46 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>21</v>
+        <v>402</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I44" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="G44" t="s" s="2">
+      <c r="J44" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="H44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="K44" t="s" s="2">
-        <v>414</v>
+        <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6754,19 +6762,19 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
@@ -6775,7 +6783,7 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>417</v>
+        <v>133</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -6783,21 +6791,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>419</v>
+        <v>21</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -6809,17 +6817,19 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="O45" t="s" s="2">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6868,28 +6878,28 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>423</v>
+        <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -6897,10 +6907,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6908,10 +6918,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -6920,16 +6930,16 @@
         <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>206</v>
+        <v>414</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6956,11 +6966,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>428</v>
+        <v>21</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -6978,28 +6990,28 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>423</v>
+        <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7007,21 +7019,21 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>21</v>
+        <v>419</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -7033,19 +7045,17 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>431</v>
+        <v>179</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7094,19 +7104,19 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>21</v>
@@ -7115,9 +7125,235 @@
         <v>423</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Y48" s="2"/>
+      <c r="Z48" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AN49" t="s" s="2">
         <v>21</v>
       </c>
     </row>

--- a/docs/StructureDefinition-retina-diagnostic-report.xlsx
+++ b/docs/StructureDefinition-retina-diagnostic-report.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-retina-diagnostic-report.xlsx
+++ b/docs/StructureDefinition-retina-diagnostic-report.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.8.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-retina-diagnostic-report.xlsx
+++ b/docs/StructureDefinition-retina-diagnostic-report.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.0</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-retina-diagnostic-report.xlsx
+++ b/docs/StructureDefinition-retina-diagnostic-report.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-retina-diagnostic-report.xlsx
+++ b/docs/StructureDefinition-retina-diagnostic-report.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
